--- a/Distribucion/Excels/GUADIELA_capacidad.xlsx
+++ b/Distribucion/Excels/GUADIELA_capacidad.xlsx
@@ -5,15 +5,15 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joseantonio.alvarez\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vincienergies-my.sharepoint.com/personal/jose-antonio_alvarez_vinci-energies_net/Documents/SEE/Datos/Distribucion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE12DA96-03FC-4869-B279-C2183B7580B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{CE12DA96-03FC-4869-B279-C2183B7580B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5AFE6BAA-58EE-41D2-B1E2-8AE8E7D14909}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{CEAB42A4-3F7F-4126-A528-5E104AA2BBAE}"/>
   </bookViews>
   <sheets>
-    <sheet name="Mapa de Capacidades-Generacion" sheetId="1" r:id="rId1"/>
+    <sheet name="Mapa" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
